--- a/data/trans_dic/IP12-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 13,47</t>
+          <t>4,92; 13,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,3; 16,73</t>
+          <t>8,13; 17,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 14,14</t>
+          <t>5,33; 13,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 14,43</t>
+          <t>4,01; 14,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 12,5</t>
+          <t>4,5; 12,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 13,47</t>
+          <t>5,76; 13,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 10,24</t>
+          <t>3,08; 10,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 16,49</t>
+          <t>4,56; 16,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 11,26</t>
+          <t>5,67; 11,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,91; 14,11</t>
+          <t>8,07; 14,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 10,38</t>
+          <t>5,16; 10,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 13,72</t>
+          <t>5,14; 13,36</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 9,31</t>
+          <t>4,29; 9,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 11,86</t>
+          <t>5,84; 11,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,22; 14,76</t>
+          <t>7,96; 15,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 12,51</t>
+          <t>5,5; 12,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 11,1</t>
+          <t>5,62; 11,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,69; 12,91</t>
+          <t>6,43; 12,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 10,12</t>
+          <t>5,09; 10,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 13,64</t>
+          <t>5,81; 12,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 9,16</t>
+          <t>5,49; 9,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 11,47</t>
+          <t>7,07; 11,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 11,36</t>
+          <t>7,19; 11,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 11,14</t>
+          <t>6,22; 11,15</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 13,31</t>
+          <t>4,92; 12,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 13,28</t>
+          <t>5,58; 12,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 9,74</t>
+          <t>4,04; 9,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 12,66</t>
+          <t>5,24; 12,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 11,25</t>
+          <t>3,98; 11,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,32</t>
+          <t>3,53; 10,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 11,19</t>
+          <t>4,68; 11,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 10,39</t>
+          <t>4,22; 10,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 10,85</t>
+          <t>5,32; 10,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 10,23</t>
+          <t>5,49; 10,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,64</t>
+          <t>4,94; 9,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,55; 10,46</t>
+          <t>5,66; 10,68</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,93</t>
+          <t>2,38; 7,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,91</t>
+          <t>3,15; 8,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 8,22</t>
+          <t>2,8; 8,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,9</t>
+          <t>3,25; 7,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,56</t>
+          <t>1,87; 6,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 12,41</t>
+          <t>5,26; 12,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 8,22</t>
+          <t>2,4; 8,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 11,31</t>
+          <t>4,71; 11,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,64</t>
+          <t>2,62; 5,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,26</t>
+          <t>4,88; 9,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,98</t>
+          <t>3,18; 7,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,53</t>
+          <t>4,65; 8,43</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,15</t>
+          <t>5,03; 8,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,04; 10,37</t>
+          <t>7,05; 10,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,63</t>
+          <t>6,33; 9,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 8,98</t>
+          <t>5,41; 8,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,07</t>
+          <t>5,26; 8,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 10,27</t>
+          <t>6,8; 10,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,05</t>
+          <t>5,21; 8,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,74</t>
+          <t>6,25; 9,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,59</t>
+          <t>5,45; 7,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 10,0</t>
+          <t>7,37; 9,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 8,36</t>
+          <t>6,23; 8,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,73</t>
+          <t>6,28; 8,91</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9132</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17965</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11866</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4575</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9323</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13234</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7395</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5544</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>18455</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>31199</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19261</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>10119</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5227; 14067</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11933; 25413</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7012; 17672</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2305; 8162</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5464; 14737</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8404; 20166</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3826; 12437</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2799; 10233</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>12911; 25671</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>23638; 41024</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13194; 26367</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>6113; 15887</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>16058</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20242</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23323</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13265</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>20308</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>25118</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18872</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>16037</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>36365</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>45359</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>42196</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>29303</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10867; 23288</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13799; 28095</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16757; 31730</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>8764; 19418</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>14271; 28084</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>17298; 34018</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>13126; 26858</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10602; 22990</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>27855; 46227</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>35714; 57961</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>33695; 52380</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>21246; 38100</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10743</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14011</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12028</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14863</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9968</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10222</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>14044</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>14875</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>20711</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>24233</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>26072</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>29738</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>6278; 16509</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8757; 20279</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7628; 18817</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9074; 21728</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5632; 15890</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5593; 16662</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8816; 21394</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>8963; 22124</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>14306; 28460</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>17336; 33506</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18653; 35775</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>21821; 41163</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9074</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8509</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14568</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7793</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8171</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>22647</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>15738</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>24061</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>16680</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>37215</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4629; 13721</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5395; 14931</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4830; 14694</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>8939; 21598</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3853; 13102</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>9461; 21824</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4175; 15465</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>14380; 34386</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>10488; 23096</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>17156; 33081</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>11026; 24770</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>27039; 48999</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>43878</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>61292</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>55726</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>47272</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>63560</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>48482</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>59103</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>91270</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>124852</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>104208</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>106375</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>34289; 55048</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>50187; 74651</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44576; 67704</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>35978; 59317</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>38030; 57921</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>51223; 76314</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>38826; 61026</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>47607; 74856</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>76515; 107244</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>107969; 145150</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>90269; 121541</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>89665; 127135</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 13,25</t>
+          <t>5,13; 13,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,13; 17,32</t>
+          <t>8,11; 17,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 13,42</t>
+          <t>5,7; 13,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 14,19</t>
+          <t>3,78; 14,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 12,14</t>
+          <t>4,4; 12,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 13,81</t>
+          <t>5,44; 13,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 10,02</t>
+          <t>3,37; 10,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 16,65</t>
+          <t>4,44; 16,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,67; 11,28</t>
+          <t>5,71; 11,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,07; 14,01</t>
+          <t>7,99; 14,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 10,31</t>
+          <t>5,29; 10,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 13,36</t>
+          <t>5,22; 12,94</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 9,2</t>
+          <t>4,19; 9,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 11,89</t>
+          <t>6,09; 12,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 15,07</t>
+          <t>8,16; 15,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 12,19</t>
+          <t>5,25; 12,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 11,07</t>
+          <t>5,56; 11,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 12,65</t>
+          <t>6,84; 12,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 10,41</t>
+          <t>4,88; 10,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 12,59</t>
+          <t>5,84; 12,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 9,12</t>
+          <t>5,4; 9,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 11,47</t>
+          <t>6,84; 11,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 11,18</t>
+          <t>7,25; 11,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,22; 11,15</t>
+          <t>6,49; 11,24</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,94</t>
+          <t>4,84; 13,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 12,91</t>
+          <t>5,46; 12,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,96</t>
+          <t>3,84; 10,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 12,55</t>
+          <t>5,46; 13,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 11,23</t>
+          <t>4,06; 11,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 10,51</t>
+          <t>3,61; 10,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 11,35</t>
+          <t>4,78; 11,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 10,41</t>
+          <t>4,3; 10,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 10,58</t>
+          <t>5,32; 10,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 10,62</t>
+          <t>5,57; 10,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,48</t>
+          <t>4,96; 9,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 10,68</t>
+          <t>5,36; 10,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,07</t>
+          <t>2,05; 6,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,71</t>
+          <t>3,08; 8,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,51</t>
+          <t>2,76; 8,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,84</t>
+          <t>3,12; 7,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,36</t>
+          <t>1,91; 6,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 12,13</t>
+          <t>5,54; 12,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,89</t>
+          <t>2,33; 7,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 11,26</t>
+          <t>4,77; 11,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,77</t>
+          <t>2,46; 5,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 9,42</t>
+          <t>4,87; 9,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,14</t>
+          <t>3,13; 6,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,43</t>
+          <t>4,57; 8,85</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,08</t>
+          <t>5,05; 8,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,49</t>
+          <t>6,95; 10,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,62</t>
+          <t>6,34; 9,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,92</t>
+          <t>5,56; 8,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,01</t>
+          <t>5,19; 8,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,13</t>
+          <t>7,0; 10,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,19</t>
+          <t>5,14; 8,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,82</t>
+          <t>6,02; 9,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 7,64</t>
+          <t>5,58; 7,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,91</t>
+          <t>7,37; 9,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,39</t>
+          <t>6,15; 8,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,91</t>
+          <t>6,31; 8,82</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5227; 14067</t>
+          <t>5449; 14854</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11933; 25413</t>
+          <t>11898; 25426</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7012; 17672</t>
+          <t>7508; 17570</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2305; 8162</t>
+          <t>2173; 8298</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5464; 14737</t>
+          <t>5343; 15526</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8404; 20166</t>
+          <t>7940; 20268</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3826; 12437</t>
+          <t>4185; 12720</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2799; 10233</t>
+          <t>2728; 10147</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12911; 25671</t>
+          <t>12997; 25717</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23638; 41024</t>
+          <t>23388; 41209</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13194; 26367</t>
+          <t>13533; 26793</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6113; 15887</t>
+          <t>6209; 15394</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10867; 23288</t>
+          <t>10612; 22918</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13799; 28095</t>
+          <t>14392; 28670</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16757; 31730</t>
+          <t>17185; 32151</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8764; 19418</t>
+          <t>8356; 19779</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14271; 28084</t>
+          <t>14101; 28013</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17298; 34018</t>
+          <t>18397; 34140</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13126; 26858</t>
+          <t>12592; 26740</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10602; 22990</t>
+          <t>10667; 23396</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27855; 46227</t>
+          <t>27364; 46755</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35714; 57961</t>
+          <t>34565; 56097</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33695; 52380</t>
+          <t>33994; 52525</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21246; 38100</t>
+          <t>22176; 38408</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6278; 16509</t>
+          <t>6174; 17589</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8757; 20279</t>
+          <t>8579; 20363</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7628; 18817</t>
+          <t>7259; 19082</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9074; 21728</t>
+          <t>9442; 22963</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5632; 15890</t>
+          <t>5751; 15751</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5593; 16662</t>
+          <t>5717; 17386</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8816; 21394</t>
+          <t>9016; 20757</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8963; 22124</t>
+          <t>9143; 22701</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14306; 28460</t>
+          <t>14310; 28412</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17336; 33506</t>
+          <t>17567; 32936</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18653; 35775</t>
+          <t>18708; 35518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21821; 41163</t>
+          <t>20660; 39974</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4629; 13721</t>
+          <t>3970; 13356</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5395; 14931</t>
+          <t>5277; 14976</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4830; 14694</t>
+          <t>4763; 14398</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8939; 21598</t>
+          <t>8591; 22002</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3853; 13102</t>
+          <t>3943; 12961</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9461; 21824</t>
+          <t>9963; 22616</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4175; 15465</t>
+          <t>4053; 13840</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14380; 34386</t>
+          <t>14586; 34346</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10488; 23096</t>
+          <t>9858; 22861</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17156; 33081</t>
+          <t>17116; 32875</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11026; 24770</t>
+          <t>10865; 24123</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27039; 48999</t>
+          <t>26521; 51430</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34289; 55048</t>
+          <t>34365; 55556</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>50187; 74651</t>
+          <t>49428; 74848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44576; 67704</t>
+          <t>44619; 68026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35978; 59317</t>
+          <t>37016; 58539</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38030; 57921</t>
+          <t>37521; 58690</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51223; 76314</t>
+          <t>52770; 77354</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38826; 61026</t>
+          <t>38294; 60359</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>47607; 74856</t>
+          <t>45885; 72733</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>76515; 107244</t>
+          <t>78269; 107397</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>107969; 145150</t>
+          <t>107955; 144490</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90269; 121541</t>
+          <t>89092; 121457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>89665; 127135</t>
+          <t>90023; 125932</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8,88%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,6%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12,24%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9,01%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 13,99</t>
+          <t>4,42; 12,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,11; 17,32</t>
+          <t>5,37; 13,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 13,35</t>
+          <t>3,16; 10,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 14,43</t>
+          <t>4,38; 16,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 12,79</t>
+          <t>4,75; 13,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 13,88</t>
+          <t>8,3; 16,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 10,24</t>
+          <t>5,8; 14,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 16,51</t>
+          <t>4,13; 14,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,71; 11,3</t>
+          <t>5,61; 11,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 14,08</t>
+          <t>7,91; 14,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 10,47</t>
+          <t>5,26; 10,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 12,94</t>
+          <t>5,21; 13,68</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,57%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,08%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 9,05</t>
+          <t>5,84; 11,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 12,14</t>
+          <t>6,69; 12,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,16; 15,27</t>
+          <t>4,7; 10,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 12,42</t>
+          <t>5,98; 13,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,56; 11,04</t>
+          <t>4,34; 9,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 12,69</t>
+          <t>5,7; 11,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 10,36</t>
+          <t>8,22; 14,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,82</t>
+          <t>5,54; 12,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,22</t>
+          <t>5,29; 9,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 11,1</t>
+          <t>6,84; 11,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,21</t>
+          <t>7,06; 11,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,24</t>
+          <t>6,45; 11,25</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8,42%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8,92%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,37%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 13,79</t>
+          <t>3,84; 11,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 12,97</t>
+          <t>3,64; 10,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 10,1</t>
+          <t>4,64; 11,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 13,27</t>
+          <t>4,43; 10,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 11,13</t>
+          <t>5,08; 13,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 10,96</t>
+          <t>5,67; 13,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 11,01</t>
+          <t>3,77; 9,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 10,68</t>
+          <t>5,53; 12,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 10,56</t>
+          <t>5,19; 10,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 10,44</t>
+          <t>5,25; 10,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 9,41</t>
+          <t>5,03; 9,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 10,37</t>
+          <t>5,69; 10,75</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,09%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,3%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4,93%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,88</t>
+          <t>2,18; 6,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,74</t>
+          <t>5,43; 12,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 8,34</t>
+          <t>2,39; 8,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,99</t>
+          <t>5,02; 11,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,29</t>
+          <t>2,14; 6,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 12,57</t>
+          <t>2,81; 8,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,95</t>
+          <t>2,69; 8,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 11,24</t>
+          <t>3,92; 8,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,71</t>
+          <t>2,61; 5,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,36</t>
+          <t>4,98; 9,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,96</t>
+          <t>3,1; 6,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,85</t>
+          <t>4,96; 9,0</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>6,44%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>8,62%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,92%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,16</t>
+          <t>5,14; 8,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,95; 10,52</t>
+          <t>6,82; 10,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 9,67</t>
+          <t>5,06; 8,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,8</t>
+          <t>6,23; 10,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,12</t>
+          <t>5,04; 8,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,0; 10,27</t>
+          <t>7,04; 10,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,1</t>
+          <t>6,25; 9,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,55</t>
+          <t>5,78; 9,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,58; 7,65</t>
+          <t>5,44; 7,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,86</t>
+          <t>7,47; 10,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,38</t>
+          <t>6,07; 8,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 8,82</t>
+          <t>6,47; 9,05</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9323</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13234</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7395</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4489</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>9132</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>17965</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>11866</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4575</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9323</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13234</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7395</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>8640</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5449; 14854</t>
+          <t>5370; 15170</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11898; 25426</t>
+          <t>7841; 19662</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7508; 17570</t>
+          <t>3927; 12713</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2173; 8298</t>
+          <t>2215; 8321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5343; 15526</t>
+          <t>5045; 14300</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7940; 20268</t>
+          <t>12178; 24554</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4185; 12720</t>
+          <t>7637; 18614</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2728; 10147</t>
+          <t>2151; 7750</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12997; 25717</t>
+          <t>12763; 25619</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23388; 41209</t>
+          <t>23152; 41297</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13533; 26793</t>
+          <t>13456; 26546</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6209; 15394</t>
+          <t>5351; 14035</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20308</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25118</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18872</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13897</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16058</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>20242</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>23323</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13265</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20308</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25118</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18872</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29303</t>
+          <t>26245</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10612; 22918</t>
+          <t>14817; 28176</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14392; 28670</t>
+          <t>17985; 34732</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17185; 32151</t>
+          <t>12119; 26118</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8356; 19779</t>
+          <t>9416; 21733</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14101; 28013</t>
+          <t>10988; 23562</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18397; 34140</t>
+          <t>13464; 28020</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12592; 26740</t>
+          <t>17305; 31068</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10667; 23396</t>
+          <t>8060; 18375</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27364; 46755</t>
+          <t>26835; 46428</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34565; 56097</t>
+          <t>34563; 57948</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33994; 52525</t>
+          <t>33088; 53220</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22176; 38408</t>
+          <t>19551; 34092</t>
         </is>
       </c>
     </row>
@@ -1930,37 +1930,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9968</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10222</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14044</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14509</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>10743</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>14011</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>12028</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14863</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9968</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10222</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14044</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29738</t>
+          <t>29540</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6174; 17589</t>
+          <t>5436; 15914</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8579; 20363</t>
+          <t>5779; 16367</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7259; 19082</t>
+          <t>8751; 21108</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9442; 22963</t>
+          <t>8873; 21655</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5751; 15751</t>
+          <t>6485; 16979</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5717; 17386</t>
+          <t>8908; 20859</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9016; 20757</t>
+          <t>7119; 18396</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9143; 22701</t>
+          <t>9657; 22552</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14310; 28412</t>
+          <t>13967; 29192</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17567; 32936</t>
+          <t>16573; 32281</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18708; 35518</t>
+          <t>18976; 36382</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20660; 39974</t>
+          <t>21342; 40309</t>
         </is>
       </c>
     </row>
@@ -2138,37 +2138,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7793</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8171</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22509</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7945</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9074</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8509</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14568</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7793</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14986</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8171</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22647</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37215</t>
+          <t>37628</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3970; 13356</t>
+          <t>4482; 13525</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5277; 14976</t>
+          <t>9769; 22334</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4763; 14398</t>
+          <t>4153; 14300</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8591; 22002</t>
+          <t>14684; 33818</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3943; 12961</t>
+          <t>4149; 13450</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9963; 22616</t>
+          <t>4823; 15269</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4053; 13840</t>
+          <t>4650; 14193</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14586; 34346</t>
+          <t>10051; 22426</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9858; 22861</t>
+          <t>10430; 22553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17116; 32875</t>
+          <t>17493; 32525</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10865; 24123</t>
+          <t>10763; 24211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26521; 51430</t>
+          <t>27224; 49446</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>77</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>63560</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>48482</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>55404</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>43878</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>61292</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>55726</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>47272</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>47392</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>63560</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>48482</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>46649</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>106375</t>
+          <t>102053</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34365; 55556</t>
+          <t>37145; 58298</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>49428; 74848</t>
+          <t>51375; 77387</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44619; 68026</t>
+          <t>37665; 59976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37016; 58539</t>
+          <t>43666; 70112</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>37521; 58690</t>
+          <t>34308; 55512</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52770; 77354</t>
+          <t>50093; 73802</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38294; 60359</t>
+          <t>43970; 67739</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>45885; 72733</t>
+          <t>36345; 59025</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>78269; 107397</t>
+          <t>76421; 106506</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>107955; 144490</t>
+          <t>109361; 146480</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89092; 121457</t>
+          <t>87932; 121156</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>90023; 125932</t>
+          <t>85971; 120273</t>
         </is>
       </c>
     </row>
